--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1235,6 +1235,57 @@
       <c r="C52" t="inlineStr">
         <is>
           <t>2026-09-09 15:51:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:43:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-09-22 13:51:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-09-22 16:02:05</t>
         </is>
       </c>
     </row>
@@ -1499,13 +1550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF013086-1065-4337-812E-ECCA68680D14}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E298A9E5-17FA-47EF-85CC-1E56026B844A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A1714AA-9BC5-41EC-A641-296B0401A2C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A2FA660-9767-4AB4-9DFE-4C72A68C7767}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18B0B718-6963-40A7-AFCE-C476F16A1241}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39293298-9342-4D06-838F-CD3DB60D1013}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1289,274 +1289,126 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:33:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:16:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:50:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:22:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:43:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:08:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-09-28 16:20:06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
-    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E298A9E5-17FA-47EF-85CC-1E56026B844A}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A2FA660-9767-4AB4-9DFE-4C72A68C7767}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39293298-9342-4D06-838F-CD3DB60D1013}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1408,7 +1408,325 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:54:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:14:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:19:35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
+    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{779C4CFC-594E-45F8-8FB7-D24F9DD4263F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0472F66-0956-42F8-B715-4A91563A7A2C}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E3B9574-7416-4A1C-88AA-FE99277945A0}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1459,274 +1459,24 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:51:38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
-    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{779C4CFC-594E-45F8-8FB7-D24F9DD4263F}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0472F66-0956-42F8-B715-4A91563A7A2C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E3B9574-7416-4A1C-88AA-FE99277945A0}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1476,7 +1476,359 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-10-02 09:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-10-02 12:05:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-10-02 12:12:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:47:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:14:43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
+    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{826071AB-EECB-47F7-8C2A-F082304D3202}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{181A031A-BBD3-4BA0-A528-F45BDB1D5D4F}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B539F94-1B3A-4017-B279-A0AF2DCD14B4}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1558,6 +1558,57 @@
       <c r="C71" t="inlineStr">
         <is>
           <t>2026-10-06 12:14:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:51:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:40:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:51:12</t>
         </is>
       </c>
     </row>
@@ -1822,13 +1873,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{826071AB-EECB-47F7-8C2A-F082304D3202}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B076A9E-49EE-4F6D-9FC8-AFD6BC229B30}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{181A031A-BBD3-4BA0-A528-F45BDB1D5D4F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF8F88EB-FF2A-4971-BD97-F2073ADD9104}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B539F94-1B3A-4017-B279-A0AF2DCD14B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FAE3DB9-A43E-4916-9D67-7D5F9EEB7D1B}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1609,6 +1609,23 @@
       <c r="C74" t="inlineStr">
         <is>
           <t>2026-10-07 15:51:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:01:11</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1890,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B076A9E-49EE-4F6D-9FC8-AFD6BC229B30}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EA29645-EA0E-451B-A5D0-F22A8CB8E74F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF8F88EB-FF2A-4971-BD97-F2073ADD9104}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC41B055-4BD8-4135-887C-A2594D46CB21}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FAE3DB9-A43E-4916-9D67-7D5F9EEB7D1B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25D090CF-86B0-4011-AB07-3194507B525A}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1626,6 +1626,23 @@
       <c r="C75" t="inlineStr">
         <is>
           <t>2026-10-08 16:01:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:25:56</t>
         </is>
       </c>
     </row>
@@ -1890,13 +1907,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EA29645-EA0E-451B-A5D0-F22A8CB8E74F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A3D8417-8E7D-4433-AC3D-F40FD004B687}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC41B055-4BD8-4135-887C-A2594D46CB21}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFBD1073-8704-4780-8354-FF1003D8C57F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25D090CF-86B0-4011-AB07-3194507B525A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E13AF2A-996A-4953-B182-7BD70764F7D1}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1643,6 +1643,23 @@
       <c r="C76" t="inlineStr">
         <is>
           <t>2026-10-12 15:25:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:28:58</t>
         </is>
       </c>
     </row>
@@ -1907,13 +1924,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A3D8417-8E7D-4433-AC3D-F40FD004B687}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{995F617B-B7F3-442F-A4AB-1F85C1CCAED6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFBD1073-8704-4780-8354-FF1003D8C57F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268E0A87-D486-4F43-AA54-E73EF9F5A9B3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E13AF2A-996A-4953-B182-7BD70764F7D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{791C1085-FE14-487E-8CCB-A6F9DBB3CE6C}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1660,6 +1660,23 @@
       <c r="C77" t="inlineStr">
         <is>
           <t>2026-10-13 10:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:20:25</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1941,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{995F617B-B7F3-442F-A4AB-1F85C1CCAED6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A90159D-0A60-4FBB-B64B-25B04C9E79C8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268E0A87-D486-4F43-AA54-E73EF9F5A9B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0655240B-6462-483B-9749-956E95C403BB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{791C1085-FE14-487E-8CCB-A6F9DBB3CE6C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5036202A-A570-4298-916E-C1FAD1ECB934}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1677,6 +1677,23 @@
       <c r="C78" t="inlineStr">
         <is>
           <t>2026-10-13 16:20:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:04:43</t>
         </is>
       </c>
     </row>
@@ -1941,13 +1958,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A90159D-0A60-4FBB-B64B-25B04C9E79C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F77E582-AE31-4052-AD5B-6A329B788193}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0655240B-6462-483B-9749-956E95C403BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E63C5B4C-478A-4E4A-8DB8-C184489447CA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5036202A-A570-4298-916E-C1FAD1ECB934}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72EC7894-B86D-41B1-AC5C-01CA0B4D0A50}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1694,6 +1694,23 @@
       <c r="C79" t="inlineStr">
         <is>
           <t>2026-10-14 10:04:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:57:28</t>
         </is>
       </c>
     </row>
@@ -1958,13 +1975,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F77E582-AE31-4052-AD5B-6A329B788193}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E335851-F3FE-4EFF-AD12-853E966E9194}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E63C5B4C-478A-4E4A-8DB8-C184489447CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00CB2EA4-0C66-4AE4-AD43-EA0BAF03F8B7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72EC7894-B86D-41B1-AC5C-01CA0B4D0A50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFEC728E-9DE6-4FEC-9CC4-93905B290C00}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1711,6 +1711,23 @@
       <c r="C80" t="inlineStr">
         <is>
           <t>2026-10-16 08:57:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:43:13</t>
         </is>
       </c>
     </row>
@@ -1975,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E335851-F3FE-4EFF-AD12-853E966E9194}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DEA7516-015B-4644-A12D-503D45D4FB8A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00CB2EA4-0C66-4AE4-AD43-EA0BAF03F8B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12BFFE8C-D1E2-462B-ABB8-F4CEA1B67378}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFEC728E-9DE6-4FEC-9CC4-93905B290C00}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8573CC76-8439-4FE5-B788-18C79D073672}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1728,6 +1728,23 @@
       <c r="C81" t="inlineStr">
         <is>
           <t>2026-10-20 14:43:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-10-21 09:45:49</t>
         </is>
       </c>
     </row>
@@ -1992,13 +2009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DEA7516-015B-4644-A12D-503D45D4FB8A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEEC17FE-9022-439E-BC45-844B27EB186D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12BFFE8C-D1E2-462B-ABB8-F4CEA1B67378}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E74BC85E-840A-4D99-8386-D9ADB938D5D2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8573CC76-8439-4FE5-B788-18C79D073672}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B034086-2B7E-49D4-A047-4AB0D58CFE87}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1745,6 +1745,74 @@
       <c r="C82" t="inlineStr">
         <is>
           <t>2026-10-21 09:45:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:21:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:22:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:24:03</t>
         </is>
       </c>
     </row>
@@ -2009,13 +2077,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEEC17FE-9022-439E-BC45-844B27EB186D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF39E9B7-2724-4A8B-9AF7-D71E11422C70}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E74BC85E-840A-4D99-8386-D9ADB938D5D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1088D7C7-71CB-41FD-8C41-31BF907BFA62}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B034086-2B7E-49D4-A047-4AB0D58CFE87}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F8FB352-E536-4118-80AB-059F8A4E7FFC}"/>
 </file>